--- a/docs/Калькулятор. Доход 1 часа.xlsx
+++ b/docs/Калькулятор. Доход 1 часа.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{432168D9-4694-4B1F-8E18-5F1AD3433069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E060D6CE-38B3-46A6-80F1-505489480034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="1080" windowWidth="25650" windowHeight="18045" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12180" yWindow="2835" windowWidth="25650" windowHeight="18045" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Заполните жёлтые ячейки</t>
   </si>
@@ -97,6 +97,9 @@
   </si>
   <si>
     <t xml:space="preserve">Доход после налога 22%  </t>
+  </si>
+  <si>
+    <t>Внутренние коэффициенты:</t>
   </si>
 </sst>
 </file>
@@ -295,7 +298,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyProtection="1">
@@ -381,6 +384,12 @@
     <xf numFmtId="165" fontId="15" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection hidden="1"/>
@@ -405,10 +414,8 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1">
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -713,11 +720,11 @@
       <c r="A1" s="1"/>
     </row>
     <row r="2" spans="1:20" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
     </row>
     <row r="3" spans="1:20" ht="2.65" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:20" s="10" customFormat="1" x14ac:dyDescent="0.2">
@@ -725,7 +732,9 @@
       <c r="B4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="7"/>
+      <c r="C4" s="7">
+        <v>100000</v>
+      </c>
       <c r="D4" s="8"/>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
@@ -736,7 +745,7 @@
       </c>
       <c r="J4" s="9">
         <f>C8*IF(C10=A27,A28,IF(C10=B27,B28,IF(C10=C27,C28,IF(C10=D27,D28,IF(C10=E27,E28,IF(C10=F27,F28,IF(C10=G27,G28,IF(C10=H27,H28,IF(C10=I27,I28,IF(C10=J27,J28,IF(C10=K27,K28,IF(C10=L27,L28,IF(C10=C29,C30,IF(C10=D29,D30,IF(C10=E29,E30,IF(C10=F29,F30,IF(C10=G29,G30,IF(C10=H29,H30,IF(C10=I29,I30,IF(C10=J29,J30,IF(C10=K29,K30,IF(C10=L29,L30,IF(C10=C31,C32,IF(C10=D31,D32,IF(C10=E31,E32,IF(C10=F31,F32,IF(C10=G31,G32,IF(C10=H31,H32,IF(C10=I31,I32,IF(C10=J31,J32,IF(C10=K31,K32,IF(C10=L31,L32))))))))))))))))))))))))))))))))</f>
-        <v>0</v>
+        <v>3099000</v>
       </c>
       <c r="K4" s="8"/>
       <c r="L4" s="8"/>
@@ -776,7 +785,9 @@
       <c r="B6" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="13"/>
+      <c r="C6" s="13">
+        <v>160</v>
+      </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -787,7 +798,7 @@
       </c>
       <c r="J6" s="9">
         <f>C8*12*C10</f>
-        <v>0</v>
+        <v>1800000</v>
       </c>
       <c r="K6" s="5"/>
       <c r="O6" s="5"/>
@@ -823,7 +834,9 @@
       <c r="B8" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="7"/>
+      <c r="C8" s="7">
+        <v>15000</v>
+      </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
@@ -834,7 +847,7 @@
       </c>
       <c r="J8" s="9">
         <f>J4-J6</f>
-        <v>0</v>
+        <v>1299000</v>
       </c>
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
@@ -874,7 +887,9 @@
       <c r="B10" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="13"/>
+      <c r="C10" s="13">
+        <v>10</v>
+      </c>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
@@ -885,12 +900,12 @@
       </c>
       <c r="J10" s="9">
         <f>J8*0.78</f>
-        <v>0</v>
+        <v>1013220</v>
       </c>
       <c r="K10" s="5"/>
       <c r="L10" s="15" t="str">
         <f>IF(G17="","","'На работе / В бизнесе' показывает, сколько приносит")</f>
-        <v/>
+        <v>'На работе / В бизнесе' показывает, сколько приносит</v>
       </c>
       <c r="M10" s="5"/>
       <c r="N10" s="5"/>
@@ -904,132 +919,132 @@
     <row r="11" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="L11" s="15" t="str">
         <f>IF(G17="","","ваш 1 час от активной деятельности, приносящей доход.")</f>
-        <v/>
+        <v>ваш 1 час от активной деятельности, приносящей доход.</v>
       </c>
     </row>
     <row r="12" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C12" s="11"/>
     </row>
     <row r="13" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="31" t="s">
+      <c r="B13" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="31"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="31"/>
-      <c r="H13" s="31"/>
-      <c r="I13" s="31"/>
-      <c r="J13" s="31"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="33"/>
+      <c r="H13" s="33"/>
+      <c r="I13" s="33"/>
+      <c r="J13" s="33"/>
       <c r="L13" s="15" t="str">
         <f>IF(G17="","","'В долгосрочных инвестициях' показывает, сколько приносят")</f>
-        <v/>
+        <v>'В долгосрочных инвестициях' показывает, сколько приносят</v>
       </c>
     </row>
     <row r="14" spans="1:20" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="31"/>
-      <c r="C14" s="31"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="31"/>
-      <c r="H14" s="31"/>
-      <c r="I14" s="31"/>
-      <c r="J14" s="31"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="33"/>
+      <c r="I14" s="33"/>
+      <c r="J14" s="33"/>
       <c r="K14" s="5"/>
       <c r="L14" s="15" t="str">
         <f>IF(G17="","","долгосрочные инвестиции, на которые вы тратите 1 час в год.")</f>
-        <v/>
+        <v>долгосрочные инвестиции, на которые вы тратите 1 час в год.</v>
       </c>
     </row>
     <row r="15" spans="1:20" s="16" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="32" t="s">
+      <c r="B15" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="32"/>
+      <c r="C15" s="34"/>
       <c r="D15" s="17"/>
-      <c r="G15" s="32" t="s">
+      <c r="G15" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="H15" s="32"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="32"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
       <c r="K15" s="18"/>
-      <c r="L15" s="27" t="str">
+      <c r="L15" s="29" t="str">
         <f>IF(G17="","","Вывод: с точки зрения обмена своего времени на деньги,")</f>
-        <v/>
-      </c>
-      <c r="M15" s="27"/>
-      <c r="N15" s="27"/>
-      <c r="O15" s="27"/>
-      <c r="P15" s="27"/>
-      <c r="Q15" s="27"/>
+        <v>Вывод: с точки зрения обмена своего времени на деньги,</v>
+      </c>
+      <c r="M15" s="29"/>
+      <c r="N15" s="29"/>
+      <c r="O15" s="29"/>
+      <c r="P15" s="29"/>
+      <c r="Q15" s="29"/>
       <c r="R15" s="17"/>
       <c r="S15" s="17"/>
       <c r="T15" s="17"/>
     </row>
     <row r="16" spans="1:20" ht="15.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="32"/>
-      <c r="C16" s="32"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="32"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="32"/>
-      <c r="L16" s="27"/>
-      <c r="M16" s="27"/>
-      <c r="N16" s="27"/>
-      <c r="O16" s="27"/>
-      <c r="P16" s="27"/>
-      <c r="Q16" s="27"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="34"/>
+      <c r="I16" s="34"/>
+      <c r="J16" s="34"/>
+      <c r="L16" s="29"/>
+      <c r="M16" s="29"/>
+      <c r="N16" s="29"/>
+      <c r="O16" s="29"/>
+      <c r="P16" s="29"/>
+      <c r="Q16" s="29"/>
     </row>
     <row r="17" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="28" t="str">
+      <c r="B17" s="30">
         <f>IF(OR(C4="",C6=""),"",C4/C6)</f>
-        <v/>
-      </c>
-      <c r="C17" s="28"/>
-      <c r="G17" s="28" t="str">
+        <v>625</v>
+      </c>
+      <c r="C17" s="30"/>
+      <c r="G17" s="30">
         <f>IF(AND(C8&gt;0,C10&gt;0),J10/C10,"")</f>
-        <v/>
-      </c>
-      <c r="H17" s="28"/>
-      <c r="I17" s="28"/>
-      <c r="J17" s="28"/>
+        <v>101322</v>
+      </c>
+      <c r="H17" s="30"/>
+      <c r="I17" s="30"/>
+      <c r="J17" s="30"/>
       <c r="L17" s="15" t="str">
         <f>IF(G17="","","ни одна работа или бизнес в долгосрок не принесут столько, ")</f>
-        <v/>
+        <v xml:space="preserve">ни одна работа или бизнес в долгосрок не принесут столько, </v>
       </c>
       <c r="M17" s="19"/>
       <c r="N17" s="19"/>
       <c r="O17" s="19"/>
     </row>
     <row r="18" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="28"/>
-      <c r="C18" s="28"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
-      <c r="I18" s="28"/>
-      <c r="J18" s="28"/>
+      <c r="B18" s="30"/>
+      <c r="C18" s="30"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="30"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="30"/>
       <c r="L18" s="4" t="str">
         <f>IF(G17="","","сколько дадут долгосрочные грамотные инвестиции.")</f>
-        <v/>
+        <v>сколько дадут долгосрочные грамотные инвестиции.</v>
       </c>
       <c r="M18" s="19"/>
       <c r="N18" s="19"/>
       <c r="O18" s="19"/>
     </row>
     <row r="19" spans="1:15" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G19" s="29" t="str">
+      <c r="G19" s="31" t="str">
         <f>IF(AND(C4&gt;1,C6&gt;1,C8&gt;1,C10&gt;1),"Больше в " &amp;ROUNDUP(G17/B17,0) &amp;" раз(а)","")</f>
-        <v/>
-      </c>
-      <c r="H19" s="29"/>
-      <c r="I19" s="29"/>
-      <c r="J19" s="29"/>
+        <v>Больше в 163 раз(а)</v>
+      </c>
+      <c r="H19" s="31"/>
+      <c r="I19" s="31"/>
+      <c r="J19" s="31"/>
       <c r="L19" s="4" t="str">
         <f>IF(G17="","","Стратегий и инструментов много - важно подобрать свои.")</f>
-        <v/>
+        <v>Стратегий и инструментов много - важно подобрать свои.</v>
       </c>
       <c r="M19" s="19"/>
       <c r="N19" s="19"/>
@@ -1072,14 +1087,14 @@
       <c r="O22" s="19"/>
     </row>
     <row r="23" spans="1:15" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B23" s="33"/>
-      <c r="C23" s="34"/>
-      <c r="E23" s="33"/>
-      <c r="F23" s="33"/>
-      <c r="G23" s="33"/>
-      <c r="H23" s="33"/>
-      <c r="I23" s="33"/>
-      <c r="J23" s="33"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="28"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="27"/>
+      <c r="J23" s="27"/>
       <c r="M23" s="19"/>
       <c r="N23" s="19"/>
       <c r="O23" s="19"/>
@@ -1092,8 +1107,18 @@
       <c r="O24" s="19"/>
     </row>
     <row r="25" spans="1:15" s="4" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C25" s="23"/>
-      <c r="D25" s="24"/>
+      <c r="C25" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" s="35"/>
+      <c r="E25" s="35"/>
+      <c r="F25" s="35"/>
+      <c r="G25" s="35"/>
+      <c r="H25" s="35"/>
+      <c r="I25" s="35"/>
+      <c r="J25" s="35"/>
+      <c r="K25" s="35"/>
+      <c r="L25" s="35"/>
       <c r="M25" s="19"/>
       <c r="N25" s="19"/>
       <c r="O25" s="19"/>
@@ -4513,7 +4538,8 @@
       <c r="T267" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
+    <mergeCell ref="C25:L25"/>
     <mergeCell ref="L15:Q16"/>
     <mergeCell ref="B17:C18"/>
     <mergeCell ref="G17:J18"/>
